--- a/data_files/Gasoline_model_simple.xlsx
+++ b/data_files/Gasoline_model_simple.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utoronto-my.sharepoint.com/personal/thiago_rodrigues_utoronto_ca/Documents/UofT/renewable_supply/data_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thiagorodrigues/Documents/CANOE/CANOE_geospatial/data_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{A1568E74-FF0D-4C69-9E5F-1B6D2F963F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AD38572-49EF-4242-9B6C-63424BA9C204}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CFDFE00-1E1C-724F-A8EF-7CC453984C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-1460" windowWidth="19200" windowHeight="21100" tabRatio="832" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="68800" yWindow="5820" windowWidth="30240" windowHeight="18880" tabRatio="832" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guidlines" sheetId="13" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="188">
   <si>
     <t>CAPEX</t>
   </si>
@@ -823,9 +823,6 @@
     <t>Electricity Transport</t>
   </si>
   <si>
-    <t>LCOH (EUR/kg hydrogen) --&gt; 3.26+51.2*LCOE</t>
-  </si>
-  <si>
     <t>The hydorgen production cost depends on the LCOE</t>
   </si>
   <si>
@@ -845,6 +842,34 @@
   </si>
   <si>
     <t>Max_Elec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR to be converted to CAD $ </t>
+  </si>
+  <si>
+    <t>X = Tons of Gasoline</t>
+  </si>
+  <si>
+    <r>
+      <t>LCOH (EUR/kg hydrogen) --&gt; 3.26 + 51.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>kWh</t>
+    </r>
+  </si>
+  <si>
+    <t>Output here is in kg to be converted to Tons</t>
+  </si>
+  <si>
+    <t>$/kWh To be converted to $MWh</t>
+  </si>
+  <si>
+    <t>Demand (tons)</t>
   </si>
 </sst>
 </file>
@@ -855,7 +880,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -901,6 +926,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri (Body)"/>
     </font>
   </fonts>
   <fills count="14">
@@ -1333,7 +1370,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1511,6 +1548,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -2236,6 +2275,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2243,7 +2283,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2966,6 +3005,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2973,7 +3013,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4192,8 +4231,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="686858" y="1816100"/>
-          <a:ext cx="14948959" cy="3198989"/>
+          <a:off x="683905" y="1765891"/>
+          <a:ext cx="14958803" cy="3109728"/>
           <a:chOff x="95250" y="1724024"/>
           <a:chExt cx="13249275" cy="3086100"/>
         </a:xfrm>
@@ -7962,7 +8001,7 @@
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B28" s="55" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C28" s="38" t="s">
         <v>168</v>
@@ -8012,10 +8051,10 @@
         <v>155</v>
       </c>
       <c r="I29" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J29" s="44" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K29" s="47" t="s">
         <v>173</v>
@@ -8048,12 +8087,28 @@
         <v>161</v>
       </c>
       <c r="J30" s="45" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="K30" s="48" t="s">
         <v>165</v>
       </c>
       <c r="L30" s="54"/>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D31" s="77" t="s">
+        <v>182</v>
+      </c>
+      <c r="J31" s="77" t="s">
+        <v>185</v>
+      </c>
+      <c r="L31" s="77" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D32" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="42" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G42" s="56" t="s">
@@ -8063,7 +8118,7 @@
     </row>
     <row r="43" spans="7:8" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G43" s="51" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H43" s="51"/>
     </row>
@@ -8364,6 +8419,9 @@
       <c r="D22" s="10" t="s">
         <v>31</v>
       </c>
+      <c r="E22" s="78" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
@@ -10792,13 +10850,13 @@
         <v>30</v>
       </c>
       <c r="C1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" t="s">
         <v>180</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>181</v>
-      </c>
-      <c r="E1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
